--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121352552</v>
+        <v>121352609</v>
       </c>
       <c r="B3" t="n">
         <v>56563</v>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,21 +846,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snägdåsen, Mpd</t>
+          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617848</v>
+        <v>617913</v>
       </c>
       <c r="R3" t="n">
-        <v>6936073</v>
+        <v>6936038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -915,18 +911,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121352609</v>
+        <v>121352552</v>
       </c>
       <c r="B4" t="n">
-        <v>56560</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,17 +968,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
+          <t>Snägdåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617913</v>
+        <v>617848</v>
       </c>
       <c r="R4" t="n">
-        <v>6936038</v>
+        <v>6936073</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1041,7 +1037,11 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121352609</v>
+        <v>121352552</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,17 +846,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
+          <t>Snägdåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617913</v>
+        <v>617848</v>
       </c>
       <c r="R3" t="n">
-        <v>6936038</v>
+        <v>6936073</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -911,14 +915,18 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121352552</v>
+        <v>121352609</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,21 +976,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snägdåsen, Mpd</t>
+          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617848</v>
+        <v>617913</v>
       </c>
       <c r="R4" t="n">
-        <v>6936073</v>
+        <v>6936038</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1041,7 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121352552</v>
+        <v>121352609</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>56563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,21 +846,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snägdåsen, Mpd</t>
+          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617848</v>
+        <v>617913</v>
       </c>
       <c r="R3" t="n">
-        <v>6936073</v>
+        <v>6936038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -915,18 +911,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121352609</v>
+        <v>121352552</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,17 +968,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
+          <t>Snägdåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617913</v>
+        <v>617848</v>
       </c>
       <c r="R4" t="n">
-        <v>6936038</v>
+        <v>6936073</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1041,7 +1037,11 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121352552</v>
+        <v>121352609</v>
       </c>
       <c r="B3" t="n">
         <v>56566</v>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,21 +846,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snägdåsen, Mpd</t>
+          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617848</v>
+        <v>617913</v>
       </c>
       <c r="R3" t="n">
-        <v>6936073</v>
+        <v>6936038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -915,18 +911,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121352609</v>
+        <v>121352552</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,17 +968,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
+          <t>Snägdåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617913</v>
+        <v>617848</v>
       </c>
       <c r="R4" t="n">
-        <v>6936038</v>
+        <v>6936073</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1041,7 +1037,11 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121352609</v>
+        <v>121352552</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,17 +846,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
+          <t>Snägdåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617913</v>
+        <v>617848</v>
       </c>
       <c r="R3" t="n">
-        <v>6936038</v>
+        <v>6936073</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -911,14 +915,18 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121352552</v>
+        <v>121352609</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>56567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,21 +976,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snägdåsen, Mpd</t>
+          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617848</v>
+        <v>617913</v>
       </c>
       <c r="R4" t="n">
-        <v>6936073</v>
+        <v>6936038</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1041,7 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>121352552</v>
       </c>
       <c r="B3" t="n">
-        <v>56570</v>
+        <v>56571</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121352609</v>
       </c>
       <c r="B4" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 16244-2024 artfynd.xlsx
+++ b/artfynd/A 16244-2024 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121352552</v>
+        <v>121352609</v>
       </c>
       <c r="B3" t="n">
-        <v>56571</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,21 +846,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snägdåsen, Mpd</t>
+          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617848</v>
+        <v>617913</v>
       </c>
       <c r="R3" t="n">
-        <v>6936073</v>
+        <v>6936038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -915,18 +911,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121352609</v>
+        <v>121352552</v>
       </c>
       <c r="B4" t="n">
-        <v>56568</v>
+        <v>56572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,17 +968,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snägdåsen, Rudtjärnen, Timrå, Mpd</t>
+          <t>Snägdåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617913</v>
+        <v>617848</v>
       </c>
       <c r="R4" t="n">
-        <v>6936038</v>
+        <v>6936073</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1041,7 +1037,11 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
